--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484202_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484202_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.007</v>
+        <v>5.9216</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2252</v>
+        <v>2.9218</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7819</v>
+        <v>2.9998</v>
       </c>
       <c r="G2" t="n">
         <v>2.0538</v>
@@ -610,13 +610,13 @@
         <v>3.3208</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8277</v>
+        <v>0.7422</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0869</v>
+        <v>0.7836</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2592</v>
+        <v>-0.0413</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3367</v>
+        <v>5.7005</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9026</v>
+        <v>4.2665</v>
       </c>
       <c r="F3" t="n">
         <v>1.4341</v>
@@ -688,10 +688,10 @@
         <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2283</v>
+        <v>0.1356</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1102</v>
+        <v>0.4741</v>
       </c>
       <c r="U3" t="n">
         <v>-0.3385</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3183</v>
+        <v>5.2839</v>
       </c>
       <c r="E4" t="n">
-        <v>2.187</v>
+        <v>3.0115</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1313</v>
+        <v>2.2725</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3051</v>
+        <v>3.0102</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9547</v>
+        <v>1.9442</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3504</v>
+        <v>1.0659</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6593</v>
+        <v>4.1085</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5784</v>
+        <v>2.9074</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0809</v>
+        <v>1.2011</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3542</v>
+        <v>-1.0984</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6237</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2694</v>
+        <v>-0.1352</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3441</v>
+        <v>2.9301</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>3.1255</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6691</v>
+        <v>0.3399</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4458</v>
+        <v>0.4266</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2233</v>
+        <v>-0.0867</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>-1.3283</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2844</v>
+        <v>4.5899</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2025</v>
+        <v>3.8601</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0818</v>
+        <v>0.7299</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0102</v>
+        <v>3.7343</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9442</v>
+        <v>1.4674</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0659</v>
+        <v>2.2669</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1085</v>
+        <v>5.7776</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9074</v>
+        <v>1.352</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2011</v>
+        <v>4.4256</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0984</v>
+        <v>-2.0433</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9631999999999999</v>
+        <v>0.1154</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1352</v>
+        <v>-2.1587</v>
       </c>
       <c r="P5" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R5" t="n">
         <v>2.9301</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.1255</v>
-      </c>
       <c r="S5" t="n">
-        <v>-0.6597</v>
+        <v>0.0743</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3823</v>
+        <v>0.2312</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2774</v>
+        <v>-0.1569</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6116</v>
+        <v>4.2015</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9906</v>
+        <v>2.2881</v>
       </c>
       <c r="F6" t="n">
-        <v>0.621</v>
+        <v>1.9134</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7343</v>
+        <v>1.3051</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4674</v>
+        <v>0.9547</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2669</v>
+        <v>0.3504</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7776</v>
+        <v>1.6593</v>
       </c>
       <c r="K6" t="n">
-        <v>1.352</v>
+        <v>1.5784</v>
       </c>
       <c r="L6" t="n">
-        <v>4.4256</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0433</v>
+        <v>-0.3542</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1154</v>
+        <v>-0.6237</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1587</v>
+        <v>0.2694</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9301</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9041</v>
+        <v>0.5523</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6382</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2659</v>
+        <v>0.0054</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3291</v>
+        <v>0.2523</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5747</v>
+        <v>-2.2031</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2456</v>
+        <v>2.4554</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.8331</v>
+        <v>-0.4429</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2295</v>
+        <v>-1.3866</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6036</v>
+        <v>0.9437</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0366</v>
+        <v>-0.9022</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9171</v>
+        <v>-1.7115</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1194</v>
+        <v>0.8093</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7966</v>
+        <v>0.4593</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3123</v>
+        <v>0.3249</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4842</v>
+        <v>0.1344</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7348</v>
+        <v>1.7581</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
         <v>2.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4274</v>
+        <v>-0.0667</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8066</v>
+        <v>0.2581</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3792</v>
+        <v>-0.3247</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2992</v>
+        <v>0.0635</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.119</v>
+        <v>0.1185</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8198</v>
+        <v>-0.055</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3741</v>
+        <v>-3.8331</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3485</v>
+        <v>-2.2295</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0257</v>
+        <v>-1.6036</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.6145</v>
+        <v>-1.0366</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.9382</v>
+        <v>-0.9171</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3237</v>
+        <v>-0.1194</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7597</v>
+        <v>-2.7966</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5897</v>
+        <v>-1.3123</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3494</v>
+        <v>-1.4842</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>3.5162</v>
+        <v>2.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7309</v>
+        <v>1.1618</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6675</v>
+        <v>1.3504</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9366</v>
+        <v>-0.1886</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3582</v>
+        <v>-0.2912</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4872</v>
+        <v>-0.5026</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8454</v>
+        <v>0.2114</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.215</v>
+        <v>-0.7926</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3226</v>
+        <v>0.1517</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1076</v>
+        <v>-0.9443</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4184</v>
+        <v>-0.5171</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0384</v>
+        <v>-0.6524</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4568</v>
+        <v>0.1352</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6334</v>
+        <v>-0.2755</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2842</v>
+        <v>0.8041</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3492</v>
+        <v>-1.0795</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1574</v>
+        <v>-0.28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0689</v>
+        <v>0.0145</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0885</v>
+        <v>-0.2945</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3622</v>
+        <v>-0.6167</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7087</v>
+        <v>1.4467</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3465</v>
+        <v>-2.0633</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4429</v>
+        <v>-0.215</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3866</v>
+        <v>-0.3226</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9437</v>
+        <v>0.1076</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9022</v>
+        <v>1.4184</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7115</v>
+        <v>-0.0384</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8093</v>
+        <v>1.4568</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4593</v>
+        <v>-1.6334</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3249</v>
+        <v>-0.2842</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1344</v>
+        <v>-1.3492</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9301</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6812</v>
+        <v>-0.1011</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2475</v>
+        <v>0.0283</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4337</v>
+        <v>-0.1294</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9962</v>
+        <v>-0.8865</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6093</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5401</v>
+        <v>-0.8436</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.806</v>
+        <v>-2.8268</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2659</v>
+        <v>1.9832</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7926</v>
+        <v>-3.3741</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1517</v>
+        <v>-2.3485</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9443</v>
+        <v>-1.0257</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5171</v>
+        <v>-2.6145</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6524</v>
+        <v>-2.9382</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1352</v>
+        <v>0.3237</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2755</v>
+        <v>-0.7597</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8041</v>
+        <v>0.5897</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0795</v>
+        <v>-1.3494</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>3.5162</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5288</v>
+        <v>0.1865</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2888</v>
+        <v>0.9597</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.24</v>
+        <v>-0.7732</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1854</v>
+        <v>-2.8173</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7729</v>
+        <v>-3.9146</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5875</v>
+        <v>1.0973</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4752</v>
@@ -1390,13 +1390,13 @@
         <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7668</v>
+        <v>1.1349</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6824</v>
+        <v>0.5407</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0844</v>
+        <v>0.5942</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3283</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.142</v>
+        <v>21.4444</v>
       </c>
       <c r="E13" t="n">
-        <v>8.1632</v>
+        <v>8.466099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>12.9788</v>
+        <v>12.9787</v>
       </c>
       <c r="G13" t="n">
-        <v>5.445300000000002</v>
+        <v>5.445299999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0485000000000001</v>
+        <v>0.04849999999999965</v>
       </c>
       <c r="I13" t="n">
         <v>5.3968</v>
@@ -1468,13 +1468,13 @@
         <v>27.348</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5772</v>
+        <v>3.8797</v>
       </c>
       <c r="T13" t="n">
-        <v>5.311500000000001</v>
+        <v>5.6141</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7343</v>
+        <v>-1.7342</v>
       </c>
       <c r="V13" t="n">
         <v>-4.4844</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.641</v>
+        <v>2.033</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3456</v>
+        <v>1.739</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2954</v>
+        <v>0.294</v>
       </c>
       <c r="G14" t="n">
         <v>2.2339</v>
@@ -1546,13 +1546,13 @@
         <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6025</v>
+        <v>-0.0055</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8035</v>
+        <v>0.1968</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.201</v>
+        <v>-0.2023</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.133</v>
+        <v>-0.1662</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1452</v>
+        <v>1.57</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0123</v>
+        <v>-1.7362</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.2747</v>
+        <v>0.9942</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1975</v>
+        <v>1.3313</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0772</v>
+        <v>-0.3371</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1854</v>
+        <v>3.6561</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5921999999999999</v>
+        <v>2.374</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.2821</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0893</v>
+        <v>-2.6619</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3948</v>
+        <v>-1.0427</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.484</v>
+        <v>-1.6192</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>-2.3441</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>2.337</v>
+        <v>0.0117</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2122</v>
+        <v>0.2581</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1248</v>
+        <v>-0.2464</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3204</v>
+        <v>-0.4021</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4689</v>
+        <v>-0.0486</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7894</v>
+        <v>-0.3535</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9942</v>
+        <v>-0.7244</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3313</v>
+        <v>1.636</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3371</v>
+        <v>-2.3604</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6561</v>
+        <v>0.8393</v>
       </c>
       <c r="K16" t="n">
-        <v>2.374</v>
+        <v>1.3111</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2821</v>
+        <v>-0.4718</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6619</v>
+        <v>-1.5638</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0427</v>
+        <v>0.3249</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6192</v>
+        <v>-1.8887</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-2.3441</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1425</v>
+        <v>0.2442</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1569</v>
+        <v>0.2841</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2995</v>
+        <v>-0.04</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5175</v>
+        <v>-0.5622</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0525</v>
+        <v>-0.6737</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5701000000000001</v>
+        <v>0.1115</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7244</v>
+        <v>-0.4136</v>
       </c>
       <c r="H17" t="n">
-        <v>1.636</v>
+        <v>0.2203</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3604</v>
+        <v>-0.6338</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8393</v>
+        <v>-0.6132</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3111</v>
+        <v>0.0205</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4718</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5638</v>
+        <v>0.1996</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3249</v>
+        <v>0.1998</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8887</v>
+        <v>-0.0002</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1288</v>
+        <v>-0.1486</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3853</v>
+        <v>-0.0605</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2565</v>
+        <v>-0.0881</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.745</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6737</v>
+        <v>-1.0175</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1322</v>
+        <v>0.2725</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4136</v>
+        <v>0.5558</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2203</v>
+        <v>0.2996</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6338</v>
+        <v>0.2562</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6132</v>
+        <v>0.376</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0205</v>
+        <v>0.3888</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.0128</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1996</v>
+        <v>0.1798</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1998</v>
+        <v>-0.0893</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0002</v>
+        <v>0.269</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3924</v>
+        <v>-0.4375</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0605</v>
+        <v>-0.2214</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3318</v>
+        <v>-0.2161</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1545</v>
+        <v>-1.1092</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4221</v>
+        <v>-0.321</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.7883</v>
       </c>
       <c r="G19" t="n">
         <v>-2.763</v>
@@ -1936,13 +1936,13 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5387</v>
+        <v>0.5839</v>
       </c>
       <c r="T19" t="n">
-        <v>0.399</v>
+        <v>0.5002</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1396</v>
+        <v>0.0838</v>
       </c>
       <c r="V19" t="n">
         <v>2.4373</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2767</v>
+        <v>-1.2236</v>
       </c>
       <c r="E20" t="n">
         <v>-1.0364</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2403</v>
+        <v>-0.1872</v>
       </c>
       <c r="G20" t="n">
         <v>0.0517</v>
@@ -2014,13 +2014,13 @@
         <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.547</v>
+        <v>-0.4939</v>
       </c>
       <c r="T20" t="n">
         <v>-0.121</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.426</v>
+        <v>-0.3728</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4593</v>
+        <v>-1.3075</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2197</v>
+        <v>-1.5609</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2396</v>
+        <v>0.2533</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5558</v>
+        <v>-2.2747</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2996</v>
+        <v>-0.1975</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2562</v>
+        <v>-2.0772</v>
       </c>
       <c r="J21" t="n">
-        <v>0.376</v>
+        <v>-1.1854</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3888</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0128</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1798</v>
+        <v>-1.0893</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0893</v>
+        <v>0.3948</v>
       </c>
       <c r="O21" t="n">
-        <v>0.269</v>
+        <v>-1.484</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1518</v>
+        <v>1.1625</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4237</v>
+        <v>0.7966</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7282</v>
+        <v>0.3658</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0727</v>
+        <v>-2.7615</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3589</v>
+        <v>-2.5611</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7138</v>
+        <v>-0.2004</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9966</v>
@@ -2170,13 +2170,13 @@
         <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3181</v>
+        <v>-0.0069</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3853</v>
+        <v>0.183</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7033</v>
+        <v>-0.1899</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.454</v>
+        <v>-3.225</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.46</v>
+        <v>-1.8533</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.994</v>
+        <v>-1.3716</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8427</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2402</v>
+        <v>-1.0111</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8941</v>
+        <v>-0.2874</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3461</v>
+        <v>-0.7238</v>
       </c>
       <c r="V23" t="n">
         <v>0.3869</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9106</v>
+        <v>-3.7725</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0176</v>
+        <v>-4.3098</v>
       </c>
       <c r="F24" t="n">
-        <v>0.107</v>
+        <v>0.5374</v>
       </c>
       <c r="G24" t="n">
         <v>-0.141</v>
@@ -2326,13 +2326,13 @@
         <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5502</v>
+        <v>-0.4121</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8941</v>
+        <v>-0.1863</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6562</v>
+        <v>-0.2258</v>
       </c>
       <c r="V24" t="n">
         <v>1.2735</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6783</v>
+        <v>-4.5296</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5122</v>
+        <v>-2.9055</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1661</v>
+        <v>-1.6241</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1249</v>
@@ -2404,13 +2404,13 @@
         <v>0.586</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8419</v>
+        <v>0.3068</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2145</v>
+        <v>0.3921</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6274</v>
+        <v>-0.0854</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.1419</v>
+        <v>-17.7714</v>
       </c>
       <c r="E26" t="n">
         <v>-12.9788</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.1632</v>
+        <v>-4.7926</v>
       </c>
       <c r="G26" t="n">
         <v>-5.4453</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0485000000000011</v>
+        <v>-0.04850000000000021</v>
       </c>
       <c r="I26" t="n">
         <v>-5.3967</v>
@@ -2482,13 +2482,13 @@
         <v>10.7437</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.5771</v>
+        <v>-0.2065000000000001</v>
       </c>
       <c r="T26" t="n">
         <v>1.7343</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.311599999999999</v>
+        <v>-1.941</v>
       </c>
       <c r="V26" t="n">
         <v>4.4847</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484202_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484202_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,387 +714,412 @@
       </c>
       <c r="X3" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2839</v>
+        <v>4.5899</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0115</v>
+        <v>3.8601</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2725</v>
+        <v>0.7299</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0102</v>
+        <v>3.7343</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9442</v>
+        <v>1.4674</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0659</v>
+        <v>2.2669</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1085</v>
+        <v>5.7776</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9074</v>
+        <v>1.352</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2011</v>
+        <v>4.4256</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0984</v>
+        <v>-2.0433</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9631999999999999</v>
+        <v>0.1154</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1352</v>
+        <v>-2.1587</v>
       </c>
       <c r="P4" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.9301</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.1255</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.3399</v>
+        <v>0.0743</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4266</v>
+        <v>0.2312</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0867</v>
+        <v>-0.1569</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5899</v>
+        <v>4.2015</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8601</v>
+        <v>2.2881</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7299</v>
+        <v>1.9134</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7343</v>
+        <v>1.3051</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4674</v>
+        <v>0.9547</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2669</v>
+        <v>0.3504</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7776</v>
+        <v>1.6593</v>
       </c>
       <c r="K5" t="n">
-        <v>1.352</v>
+        <v>1.5784</v>
       </c>
       <c r="L5" t="n">
-        <v>4.4256</v>
+        <v>0.0809</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0433</v>
+        <v>-0.3542</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1154</v>
+        <v>-0.6237</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1587</v>
+        <v>0.2694</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9301</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0743</v>
+        <v>0.5523</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2312</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1569</v>
+        <v>0.0054</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2015</v>
+        <v>3.149</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2881</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9134</v>
+        <v>2.2725</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3051</v>
+        <v>0.8752</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9547</v>
+        <v>1.0233</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3504</v>
+        <v>-0.148</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6593</v>
+        <v>1.9736</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5784</v>
+        <v>1.9864</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0809</v>
+        <v>-0.0128</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3542</v>
+        <v>-1.0984</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6237</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2694</v>
+        <v>-0.1352</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3441</v>
+        <v>2.9301</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>3.1255</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5523</v>
+        <v>0.3399</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.4266</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0054</v>
+        <v>-0.0867</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>-1.3283</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2523</v>
+        <v>2.1349</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2031</v>
+        <v>2.1349</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4429</v>
+        <v>2.1349</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3866</v>
+        <v>0.921</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9437</v>
+        <v>1.214</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9022</v>
+        <v>2.1349</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7115</v>
+        <v>0.921</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8093</v>
+        <v>1.214</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4593</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3249</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0667</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2581</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3247</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0635</v>
+        <v>0.914</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1185</v>
+        <v>0.914</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.055</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8331</v>
+        <v>0.914</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2295</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6036</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0366</v>
+        <v>0.914</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9171</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1194</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7966</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3123</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4842</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1618</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3504</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1886</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,75 +1129,80 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2912</v>
+        <v>0.0635</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5026</v>
+        <v>0.1185</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2114</v>
+        <v>-0.055</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7926</v>
+        <v>-3.8331</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1517</v>
+        <v>-2.2295</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9443</v>
+        <v>-1.6036</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5171</v>
+        <v>-1.0366</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6524</v>
+        <v>-0.9171</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1352</v>
+        <v>-0.1194</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2755</v>
+        <v>-2.7966</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8041</v>
+        <v>-1.3123</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0795</v>
+        <v>-1.4842</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>2.7348</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>2.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.28</v>
+        <v>1.1618</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0145</v>
+        <v>1.3504</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2945</v>
+        <v>-0.1886</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,480 +1212,511 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6167</v>
+        <v>-0.2912</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4467</v>
+        <v>-0.5026</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0633</v>
+        <v>0.2114</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.215</v>
+        <v>-0.7926</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3226</v>
+        <v>0.1517</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1076</v>
+        <v>-0.9443</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4184</v>
+        <v>-0.5171</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0384</v>
+        <v>-0.6524</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4568</v>
+        <v>0.1352</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6334</v>
+        <v>-0.2755</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2842</v>
+        <v>0.8041</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3492</v>
+        <v>-1.0795</v>
       </c>
       <c r="P10" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1011</v>
+        <v>-0.28</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0283</v>
+        <v>0.0145</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1294</v>
+        <v>-0.2945</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8436</v>
+        <v>-0.6167</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8268</v>
+        <v>1.4467</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9832</v>
+        <v>-2.0633</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3741</v>
+        <v>-0.215</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3485</v>
+        <v>-0.3226</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0257</v>
+        <v>0.1076</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6145</v>
+        <v>1.4184</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.9382</v>
+        <v>-0.0384</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3237</v>
+        <v>1.4568</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7597</v>
+        <v>-1.6334</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5897</v>
+        <v>-0.2842</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3494</v>
+        <v>-1.3492</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5162</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1865</v>
+        <v>-0.1011</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9597</v>
+        <v>0.0283</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7732</v>
+        <v>-0.1294</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8173</v>
+        <v>-0.6617</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9146</v>
+        <v>-3.1171</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0973</v>
+        <v>2.4554</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4752</v>
+        <v>-1.3568</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.65</v>
+        <v>-1.6936</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1749</v>
+        <v>0.3368</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8933</v>
+        <v>-1.8162</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0435</v>
+        <v>-2.0185</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8498</v>
+        <v>0.2023</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3684</v>
+        <v>0.4593</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6935</v>
+        <v>0.3249</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.1344</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.2975</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1488</v>
+        <v>2.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1349</v>
+        <v>-0.0667</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5407</v>
+        <v>0.2581</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5942</v>
+        <v>-0.3247</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3283</v>
+        <v>-0.9962</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.0511</v>
+        <v>-0.3869</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.4444</v>
+        <v>-0.8436</v>
       </c>
       <c r="E13" t="n">
-        <v>8.466099999999999</v>
+        <v>-2.8268</v>
       </c>
       <c r="F13" t="n">
-        <v>12.9787</v>
+        <v>1.9832</v>
       </c>
       <c r="G13" t="n">
-        <v>5.445299999999999</v>
+        <v>-3.3741</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04849999999999965</v>
+        <v>-2.3485</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3968</v>
+        <v>-1.0257</v>
       </c>
       <c r="J13" t="n">
-        <v>16.0848</v>
+        <v>-2.6145</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9158</v>
+        <v>-2.9382</v>
       </c>
       <c r="L13" t="n">
-        <v>14.1689</v>
+        <v>0.3237</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.6396</v>
+        <v>-0.7597</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8673</v>
+        <v>0.5897</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.772199999999998</v>
+        <v>-1.3494</v>
       </c>
       <c r="P13" t="n">
-        <v>16.6041</v>
+        <v>2.3441</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.7438</v>
+        <v>-1.1721</v>
       </c>
       <c r="R13" t="n">
-        <v>27.348</v>
+        <v>3.5162</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8797</v>
+        <v>0.1865</v>
       </c>
       <c r="T13" t="n">
-        <v>5.6141</v>
+        <v>0.9597</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7342</v>
+        <v>-0.7732</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.4844</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.4891</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9953</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.033</v>
+        <v>-2.8173</v>
       </c>
       <c r="E14" t="n">
-        <v>1.739</v>
+        <v>-3.9146</v>
       </c>
       <c r="F14" t="n">
-        <v>0.294</v>
+        <v>1.0973</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2339</v>
+        <v>-0.4752</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9911</v>
+        <v>-0.65</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2428</v>
+        <v>0.1749</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7142</v>
+        <v>0.8933</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7176</v>
+        <v>0.0435</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9966</v>
+        <v>0.8498</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4803</v>
+        <v>-1.3684</v>
       </c>
       <c r="N14" t="n">
-        <v>1.2735</v>
+        <v>-0.6935</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7538</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-4.2975</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0055</v>
+        <v>1.1349</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1968</v>
+        <v>0.5407</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2023</v>
+        <v>0.5942</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.3283</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.0511</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1662</v>
+        <v>21.4444</v>
       </c>
       <c r="E15" t="n">
-        <v>1.57</v>
+        <v>8.465999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7362</v>
+        <v>12.9787</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9942</v>
+        <v>5.445300000000002</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3313</v>
+        <v>0.04860000000000031</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3371</v>
+        <v>5.396999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6561</v>
+        <v>16.0848</v>
       </c>
       <c r="K15" t="n">
-        <v>2.374</v>
+        <v>1.915799999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2821</v>
+        <v>14.169</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6619</v>
+        <v>-10.6396</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0427</v>
+        <v>-1.8673</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6192</v>
+        <v>-8.772199999999998</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1721</v>
+        <v>16.6041</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3441</v>
+        <v>-10.7438</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>27.348</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0117</v>
+        <v>3.8797</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2581</v>
+        <v>5.614100000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2464</v>
+        <v>-1.7342</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-4.4844</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-2.4891</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.9953</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4021</v>
+        <v>2.033</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0486</v>
+        <v>1.739</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3535</v>
+        <v>0.294</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7244</v>
+        <v>2.2339</v>
       </c>
       <c r="H16" t="n">
-        <v>1.636</v>
+        <v>1.9911</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.3604</v>
+        <v>0.2428</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8393</v>
+        <v>2.7142</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3111</v>
+        <v>0.7176</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4718</v>
+        <v>1.9966</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5638</v>
+        <v>-0.4803</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3249</v>
+        <v>1.2735</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8887</v>
+        <v>-1.7538</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2442</v>
+        <v>-0.0055</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2841</v>
+        <v>0.1968</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.04</v>
+        <v>-0.2023</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1811,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5622</v>
+        <v>0.614</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6737</v>
+        <v>0.614</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1115</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4136</v>
+        <v>0.614</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2203</v>
+        <v>0.614</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6338</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6132</v>
+        <v>0.614</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0205</v>
+        <v>0.614</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1996</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1998</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,13 +1856,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1486</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0605</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0881</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1894,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.745</v>
+        <v>-0.4021</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0175</v>
+        <v>-0.0486</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2725</v>
+        <v>-0.3535</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5558</v>
+        <v>-0.7244</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2996</v>
+        <v>1.636</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2562</v>
+        <v>-2.3604</v>
       </c>
       <c r="J18" t="n">
-        <v>0.376</v>
+        <v>0.8393</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3888</v>
+        <v>1.3111</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0128</v>
+        <v>-0.4718</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1798</v>
+        <v>-1.5638</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0893</v>
+        <v>0.3249</v>
       </c>
       <c r="O18" t="n">
-        <v>0.269</v>
+        <v>-1.8887</v>
       </c>
       <c r="P18" t="n">
         <v>-0.586</v>
@@ -1858,28 +1939,33 @@
         <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4375</v>
+        <v>0.2442</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2214</v>
+        <v>0.2841</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2161</v>
+        <v>-0.04</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1092</v>
+        <v>-0.5622</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.321</v>
+        <v>-0.6737</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7883</v>
+        <v>0.1115</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.763</v>
+        <v>-0.4136</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.493</v>
+        <v>0.2203</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.27</v>
+        <v>-0.6338</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4455</v>
+        <v>-0.6132</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7946</v>
+        <v>0.0205</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3492</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3176</v>
+        <v>0.1996</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6984</v>
+        <v>0.1998</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6192</v>
+        <v>-0.0002</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5839</v>
+        <v>-0.1486</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5002</v>
+        <v>-0.0605</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0838</v>
+        <v>-0.0881</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2236</v>
+        <v>-0.745</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0364</v>
+        <v>-1.0175</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1872</v>
+        <v>0.2725</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0517</v>
+        <v>0.5558</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4876</v>
+        <v>0.2996</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5393</v>
+        <v>0.2562</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0614</v>
+        <v>0.376</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0614</v>
+        <v>0.3888</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.0128</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0097</v>
+        <v>0.1798</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.549</v>
+        <v>-0.0893</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5393</v>
+        <v>0.269</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4939</v>
+        <v>-0.4375</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.121</v>
+        <v>-0.2214</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3728</v>
+        <v>-0.2161</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3075</v>
+        <v>-0.7802</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5609</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2533</v>
+        <v>-1.7362</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2747</v>
+        <v>0.3802</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1975</v>
+        <v>0.7173</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0772</v>
+        <v>-0.3371</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1854</v>
+        <v>3.0421</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5921999999999999</v>
+        <v>1.7601</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.2821</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0893</v>
+        <v>-2.6619</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3948</v>
+        <v>-1.0427</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.484</v>
+        <v>-1.6192</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-2.3441</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1625</v>
+        <v>0.0117</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7966</v>
+        <v>0.2581</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3658</v>
+        <v>-0.2464</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7615</v>
+        <v>-1.1092</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5611</v>
+        <v>-0.321</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2004</v>
+        <v>-0.7883</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9966</v>
+        <v>-2.763</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3359</v>
+        <v>-2.493</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6607</v>
+        <v>-0.27</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5767</v>
+        <v>-0.4455</v>
       </c>
       <c r="K22" t="n">
-        <v>0.023</v>
+        <v>-1.7946</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5537</v>
+        <v>1.3492</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5733</v>
+        <v>-2.3176</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3589</v>
+        <v>-0.6984</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2144</v>
+        <v>-1.6192</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7581</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.3208</v>
+        <v>-2.1488</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0069</v>
+        <v>0.5839</v>
       </c>
       <c r="T22" t="n">
-        <v>0.183</v>
+        <v>0.5002</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1899</v>
+        <v>0.0838</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.225</v>
+        <v>-1.2236</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8533</v>
+        <v>-1.0364</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3716</v>
+        <v>-0.1872</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8427</v>
+        <v>0.0517</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6802</v>
+        <v>-0.4876</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1625</v>
+        <v>0.5393</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7549</v>
+        <v>0.0614</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2418</v>
+        <v>0.0614</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9966</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5975</v>
+        <v>-0.0097</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4384</v>
+        <v>-0.549</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1591</v>
+        <v>0.5393</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.3208</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0111</v>
+        <v>-0.4939</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2874</v>
+        <v>-0.121</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7238</v>
+        <v>-0.3728</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7725</v>
+        <v>-1.3075</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3098</v>
+        <v>-1.5609</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5374</v>
+        <v>0.2533</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.141</v>
+        <v>-2.2747</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4528</v>
+        <v>-0.1975</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5938</v>
+        <v>-2.0772</v>
       </c>
       <c r="J24" t="n">
-        <v>2.1823</v>
+        <v>-1.1854</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2123</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>1.97</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3232</v>
+        <v>-1.0893</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2405</v>
+        <v>0.3948</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.5638</v>
+        <v>-1.484</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.4929</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.251</v>
+        <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4121</v>
+        <v>1.1625</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1863</v>
+        <v>0.7966</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2258</v>
+        <v>0.3658</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2735</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.3283</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5296</v>
+        <v>-2.7615</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9055</v>
+        <v>-2.5611</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6241</v>
+        <v>-0.2004</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.1249</v>
+        <v>-0.9966</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7854</v>
+        <v>-0.3359</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6605</v>
+        <v>-0.6607</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7227</v>
+        <v>0.5767</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6127</v>
+        <v>0.023</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3354</v>
+        <v>0.5537</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8476</v>
+        <v>-1.5733</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1727</v>
+        <v>-0.3589</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-1.2144</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.7115</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.2975</v>
+        <v>-3.3208</v>
       </c>
       <c r="R25" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3068</v>
+        <v>-0.0069</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3921</v>
+        <v>0.183</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0854</v>
+        <v>-0.1899</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,318 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-3.225</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.8533</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.3716</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.8427</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.6802</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.1625</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.7549</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.2418</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.9966</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.5975</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.4384</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-2.1591</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-1.0111</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.2874</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.7238</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G. GEORGIOU</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.7725</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-4.3098</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.141</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.5938</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.1823</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2123</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-2.3232</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-2.5638</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-4.4929</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-6.251</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.4121</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1863</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2258</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.3283</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P. CABANERO PUERTAS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-4.5296</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-2.9055</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-1.6241</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.1249</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.7854</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7227</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.6127</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.3354</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1.8476</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.1727</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-3.7115</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-4.2975</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.0854</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484202_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>-17.7714</v>
       </c>
-      <c r="E26" t="n">
-        <v>-12.9788</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="E29" t="n">
+        <v>-12.9787</v>
+      </c>
+      <c r="F29" t="n">
         <v>-4.7926</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G29" t="n">
         <v>-5.4453</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H29" t="n">
         <v>-0.04850000000000021</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I29" t="n">
         <v>-5.3967</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J29" t="n">
         <v>10.6395</v>
       </c>
-      <c r="K26" t="n">
-        <v>1.8674</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K29" t="n">
+        <v>1.867499999999999</v>
+      </c>
+      <c r="L29" t="n">
         <v>8.7722</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M29" t="n">
         <v>-16.0848</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N29" t="n">
         <v>-1.9159</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O29" t="n">
         <v>-14.169</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P29" t="n">
         <v>-16.6041</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q29" t="n">
         <v>-27.3481</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R29" t="n">
         <v>10.7437</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S29" t="n">
         <v>-0.2065000000000001</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T29" t="n">
         <v>1.7343</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U29" t="n">
         <v>-1.941</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V29" t="n">
         <v>4.4847</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W29" t="n">
         <v>1.9954</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X29" t="n">
         <v>2.4892</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
